--- a/www/download/COUNTRY.SWE.rpO2.xlsx
+++ b/www/download/COUNTRY.SWE.rpO2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Suécia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>7.1209853786912</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>6.70421035800362</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>7.62718343458456</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>7.94723073282277</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>8.26104914409274</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>9.13075211422837</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>10.3114045632859</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>9.70685325223753</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>8.06776946061647</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>7.33729552481548</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>7.44934438059463</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>7.36702534389249</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>6.75082699066162</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.51703522574423</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.60913399607839</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.129</t>
+          <t>-0.921898660407276</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.096</t>
+          <t>-0.921286600787402</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.043</t>
+          <t>-0.900785163342609</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4.111</t>
+          <t>-0.909778822833431</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.198</t>
+          <t>-0.92784827646527</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.301</t>
+          <t>-0.946008228332245</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.391</t>
+          <t>-0.947426541927042</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.393</t>
+          <t>-0.946702042181105</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.368</t>
+          <t>-0.953642548960608</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4.337</t>
+          <t>-0.954386632183998</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.349</t>
+          <t>-0.958753202035848</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.423</t>
+          <t>-0.954329413073173</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4.524</t>
+          <t>-0.949281096292666</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4.542</t>
+          <t>-0.94076354753201</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4.425</t>
+          <t>-0.919918348498926</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.848</t>
+          <t>-0.892610579388682</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.819</t>
+          <t>-0.892483168808048</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.768</t>
+          <t>-0.865220042225838</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.836</t>
+          <t>-0.877774716414746</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.918</t>
+          <t>-0.902113440910329</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.023</t>
+          <t>-0.928767986123409</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.124</t>
+          <t>-0.931610014411681</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.134</t>
+          <t>-0.92977196598584</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4.128</t>
+          <t>-0.941507053931119</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4.091</t>
+          <t>-0.941069721134584</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>4.103</t>
+          <t>-0.947142011033409</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>-0.942064115967796</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>4.268</t>
+          <t>-0.936076619485636</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>4.321</t>
+          <t>-0.923690906035217</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4.228</t>
+          <t>-0.896615759008015</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6772.82</t>
+          <t>-0.88352348040416</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6770.69</t>
+          <t>-0.882044581376691</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6703.5</t>
+          <t>-0.851326857471217</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6809.79</t>
+          <t>-0.864510384360088</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6988.38</t>
+          <t>-0.891064911394907</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7061.95</t>
+          <t>-0.921289940655926</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7105.7</t>
+          <t>-0.924924688525791</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>7006.6</t>
+          <t>-0.922366710312112</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6908.1</t>
+          <t>-0.941076407331986</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6963.43</t>
+          <t>-0.935910880074954</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6979.96</t>
+          <t>-0.943048554581736</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>-0.938106920077908</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>7319.33</t>
+          <t>-0.934668632350922</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>7362.323</t>
+          <t>-0.921739339297629</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>7146.911</t>
+          <t>-0.892104544890782</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6234.64</t>
+          <t>223682387637.012</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6244.23</t>
+          <t>213272572872.82</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6174.71</t>
+          <t>165700044267.499</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6277.92</t>
+          <t>191176710816.963</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6444.15</t>
+          <t>259098929681.642</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6539.08</t>
+          <t>407255506510.521</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6609.93</t>
+          <t>397716527558.294</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6527.4</t>
+          <t>346165087690.438</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6446.22</t>
+          <t>403440518619.855</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6489.13</t>
+          <t>403439407816.781</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6490.82</t>
+          <t>454259008322.072</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6587.61</t>
+          <t>483565346946.537</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>6822.76</t>
+          <t>412661248543.3</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6920.38</t>
+          <t>342356697769.008</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6705.67</t>
+          <t>200353917452.712</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>87315021513.0411</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>89649928853.1368</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>70165726233.811</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>79426213872.2467</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>104169198309.547</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>151967459258.934</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>161767575924.628</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>23.11</t>
+          <t>157505086147.963</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>185656689802.447</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>185547431541.243</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>204678012822.479</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>200299957559.464</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>184095853011.321</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>159773406206.617</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>104395906897.119</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>56.83</t>
+          <t>28682653.838833</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>57.47</t>
+          <t>23505949.5548584</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>58.03</t>
+          <t>20671046.7491702</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>22691154.3466167</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>57.42</t>
+          <t>30591760.9719607</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>58.29</t>
+          <t>43990216.5746978</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>58.35</t>
+          <t>48598940.8227441</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>38266757.3191992</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>37799077.2527709</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>30463424.0419606</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>58.13</t>
+          <t>31974966.1605799</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>31026187.0296391</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>22404357.2146833</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>56.12</t>
+          <t>16988442.1503384</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>53.01</t>
+          <t>13841355.9654496</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>2256.08460880917</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>2397.31155811727</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>2310.13173640003</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>2315.76029863903</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>2231.97209182412</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>1819.77879689236</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>1770.01878100646</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>18.49</t>
+          <t>1861.07185709197</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>19.58</t>
+          <t>1870.40896791332</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>17.66</t>
+          <t>2026.81082894799</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>1921.47637440721</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>2151.97528637797</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>2765.80313399939</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>3025.54678131941</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>3362.38904563394</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12.74</t>
+          <t>93776.1843882961</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>92844.4740712316</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>71056.6890208239</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>80636.8037655351</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>101766.989379582</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>16.49</t>
+          <t>126157.198647279</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>17.27</t>
+          <t>117186.74626578</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>107181.810206101</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>127714.461669535</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>137951.448899722</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19.89</t>
+          <t>150151.164603036</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>21.03</t>
+          <t>169392.784831197</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>184226.629910817</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>171020.652754984</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>115590.466225942</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>58.57</t>
+          <t>-0.89805462613026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>-0.897634719939046</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>59.74</t>
+          <t>-0.871630651824366</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.24</t>
+          <t>-0.883479883110791</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>59.43</t>
+          <t>-0.907033774434369</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>60.73</t>
+          <t>-0.932795540052151</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>60.91</t>
+          <t>-0.935538009011835</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>-0.934084782446458</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>61.48</t>
+          <t>-0.945205439246915</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>61.25</t>
+          <t>-0.944720707415311</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>60.96</t>
+          <t>-0.950495399787848</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>60.36</t>
+          <t>-0.945802220950584</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>60.37</t>
+          <t>-0.940505049986884</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>59.85</t>
+          <t>-0.929656772092927</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>56.63</t>
+          <t>-0.904787518659924</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>48664.0245698599</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>53484.099109837</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>50572.9831406212</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>52046.5431885725</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>54864.259842949</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>53432.1445377011</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>48358.4082237311</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>52006.600409208</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>62542.9067994847</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>64230.6436042982</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>65520.3671164255</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>67553.0926450966</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>18.07</t>
+          <t>77102.2193546365</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7.1209853786912</t>
+          <t>22692.1933346658</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6.70421035800362</t>
+          <t>23474.0983093463</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7.62718343458456</t>
+          <t>18621.4772382726</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7.94723073282277</t>
+          <t>20703.8588932687</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8.26104914409274</t>
+          <t>26590.0547042716</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9.13075211422837</t>
+          <t>37775.5995075527</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10.3114045632859</t>
+          <t>39229.696363524</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.70685325223753</t>
+          <t>38098.0809220278</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8.06776946061647</t>
+          <t>44979.3317672368</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7.33729552481548</t>
+          <t>45352.8137322162</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>7.44934438059463</t>
+          <t>49882.5338327352</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>7.36702534389249</t>
+          <t>48028.9558698121</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>6.75082699066162</t>
+          <t>43134.9968395044</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>6.51703522574423</t>
+          <t>36978.5928684281</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>7.60913399607839</t>
+          <t>24689.5808576486</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>214222193762.259</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>217738432191.486</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>176738240990.867</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>198592985043.197</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>272244421340.805</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>379634828148.926</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>383515185436.305</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>378671920743.566</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>453464994209.994</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>490679850076.144</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>526916375909.712</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>531504772676.155</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>464692986820.002</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>425746595282.502</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>262262494772.497</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>224159319455.863</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>229234305089.021</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>187211489958.802</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>214120167485.368</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>293233946552.452</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>383030236576.169</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>386548134150.785</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>377364808412.724</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>441838623681.614</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>464858852689.812</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>485652183601.183</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>475222565117.042</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>408522403188.084</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>371804571080.221</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>225130023027.283</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>-9937125693.60389</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>-11495872897.5348</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>-10473248967.9349</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>-15527182442.1712</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-20989525211.6463</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>-3395408427.24271</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>-3032948714.4798</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>1307112330.84178</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>11626370528.3806</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>25820997386.3321</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.809</t>
+          <t>41264192308.5294</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>56282207559.1129</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.986</t>
+          <t>56170583631.9182</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53942024202.2805</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37132471745.2133</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>2313.36413342693</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.502</t>
+          <t>2402.93264761459</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>2390.42689514445</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>2412.41605830136</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>2471.9770234398</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>2538.68876411132</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>2528.82433345395</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>2511.24329234791</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.574</t>
+          <t>2464.62272715303</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>2507.0714598421</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>2469.4148949587</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>2603.06273820621</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>2566.31448078224</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2601.1935858267</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>2350.75625670317</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>2318.02299699323</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>2404.82038273846</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>2395.07928450542</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>2420.73831945967</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>2478.96493359158</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>2540.44348799356</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2528.63982598228</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>2512.75341688268</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>2474.35397503219</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>2516.88143081554</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>2487.43963544246</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>2615.79026302455</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>2579.71929057285</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>2494.20330502532</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>2462.60642984027</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-92.19</t>
+          <t>96725.5237641605</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-92.13</t>
+          <t>102366.696057867</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-90.08</t>
+          <t>101699.771226788</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-90.98</t>
+          <t>104969.377987809</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-92.78</t>
+          <t>107075.320954573</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-94.6</t>
+          <t>110832.788765628</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-94.74</t>
+          <t>100696.185240731</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-94.67</t>
+          <t>106311.677138873</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-95.36</t>
+          <t>130882.297248063</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-95.44</t>
+          <t>159190.879264687</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-95.88</t>
+          <t>170943.424743657</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-95.43</t>
+          <t>192960.40986097</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-94.93</t>
+          <t>226789.430813134</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-94.08</t>
+          <t>248132.595279107</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-91.99</t>
+          <t>181913.166040362</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-89.26</t>
+          <t>88366197926.6072</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-89.25</t>
+          <t>83194089454.9108</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-86.52</t>
+          <t>67495849170.7685</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-87.78</t>
+          <t>78264270378.577</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-90.21</t>
+          <t>109514994784.478</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-92.88</t>
+          <t>179002751049.15</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-93.16</t>
+          <t>169355815613.61</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-92.98</t>
+          <t>144846479783.918</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-94.15</t>
+          <t>174249776870.412</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-94.11</t>
+          <t>183712954577.909</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-94.71</t>
+          <t>208551295998.89</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-94.21</t>
+          <t>234257866597.821</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-93.61</t>
+          <t>194552081128.747</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-92.37</t>
+          <t>175372642484.418</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-89.66</t>
+          <t>102688025661.843</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-88.35</t>
+          <t>75831.3495973377</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-88.2</t>
+          <t>79890.6155496373</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-85.13</t>
+          <t>78082.0581520606</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-86.45</t>
+          <t>83083.1034853668</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-89.11</t>
+          <t>85453.4305373733</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-92.13</t>
+          <t>89747.980114205</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-92.49</t>
+          <t>81785.0223451439</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-92.24</t>
+          <t>85720.0656918854</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-94.11</t>
+          <t>104826.942952039</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-93.59</t>
+          <t>123953.538242074</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-94.3</t>
+          <t>136436.242345256</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-93.81</t>
+          <t>155369.566848147</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-93.47</t>
+          <t>186026.553897001</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-92.17</t>
+          <t>208723.923020259</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-89.21</t>
+          <t>152138.611332661</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>9570.885</t>
+          <t>216073508710.535</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>9849.663</t>
+          <t>211684939375.21</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>9683.785</t>
+          <t>163122830881.732</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>9952.624</t>
+          <t>194681610805.51</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>10405.951</t>
+          <t>275199877673.19</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>10925.685</t>
+          <t>410451295355.526</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11103.763</t>
+          <t>410422061370.307</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>11039.28</t>
+          <t>374913551489.439</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>10807.731</t>
+          <t>447245090404.522</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>10916.722</t>
+          <t>450607458833.29</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10817.626</t>
+          <t>505421268343.927</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>11568.332</t>
+          <t>532750066656.069</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>11671.424</t>
+          <t>471181358078.109</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>11327.789</t>
+          <t>442216131318.989</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>10896.692</t>
+          <t>268424100517.669</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>8901.363</t>
+          <t>20894.1741668229</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>9177.04</t>
+          <t>22476.0805082296</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>9007.129</t>
+          <t>23617.7130747272</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>9254.752</t>
+          <t>21886.274502442</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>9684.217</t>
+          <t>21621.8904171997</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>10212.891</t>
+          <t>21084.8086514232</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10427.86</t>
+          <t>18911.1628955872</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>10381.982</t>
+          <t>20591.611446988</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>10172.977</t>
+          <t>26055.3542960244</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>10256.931</t>
+          <t>35237.341022613</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>10132.503</t>
+          <t>34507.182398401</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>10855.813</t>
+          <t>37590.8430128234</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>10952.774</t>
+          <t>40762.8769161332</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>11238.977</t>
+          <t>39408.6722588476</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>9939.793</t>
+          <t>29774.5547077013</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>223682.388</t>
+          <t>-127707310783.928</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>213272.573</t>
+          <t>-128490849920.299</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>165700.044</t>
+          <t>-95626981710.9639</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>191176.711</t>
+          <t>-116417340426.934</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>259098.93</t>
+          <t>-165684882888.712</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>407255.507</t>
+          <t>-231448544306.376</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>397716.528</t>
+          <t>-241066245756.696</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>346165.088</t>
+          <t>-230067071705.521</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>403440.519</t>
+          <t>-272995313534.11</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>403439.408</t>
+          <t>-266894504255.382</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>454259.008</t>
+          <t>-296869972345.037</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>483565.347</t>
+          <t>-298492200058.249</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>412661.249</t>
+          <t>-276629276949.361</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>342356.698</t>
+          <t>-266843488834.571</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>200353.917</t>
+          <t>-165736074855.826</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>114854.61053</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>122774.93584</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>112054.99439</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>112549.77093</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>113330.15737</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>108058.67783</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>99019.68258</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>110070.99521</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>138070.00793</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>158839.5881</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>160076.10059</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>172003.34448</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>199903.80459</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>208735.56022</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>167415.59572</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5381.392</t>
+          <t>0.0535880004430437</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5506.852</t>
+          <t>0.0446475249065349</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5387.092</t>
+          <t>0.0447102742219196</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>5490.29</t>
+          <t>0.0425321401521922</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>5682.605</t>
+          <t>0.044700616629324</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5874.535</t>
+          <t>0.0349235375180972</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>6007.213</t>
+          <t>0.0276544014955168</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>6010.704</t>
+          <t>0.0323535428974781</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>5908.483</t>
+          <t>0.0403038827323497</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>5927.414</t>
+          <t>0.0547857361478185</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>5813.128</t>
+          <t>0.054832707452759</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>6143.241</t>
+          <t>0.0666301044100791</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>6195.303</t>
+          <t>0.0647866830108882</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>6056.673</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>5828.057</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>133127.784362746</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>150511.0878089</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>136807.643597456</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>137032.009325101</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>136351.930258648</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>135897.23871761</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>128638.440508168</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>140953.50530439</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>174679.259001201</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>198006.744264434</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>201662.713361205</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>211588.521117675</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>248571.027188134</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>262905.781776772</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>222136.709758279</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>87315.022</t>
+          <t>143141.090244378</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>89649.929</t>
+          <t>161542.668371692</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>70165.726</t>
+          <t>147085.249329839</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>79426.214</t>
+          <t>147365.163379276</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>104169.198</t>
+          <t>146513.806072053</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>151967.459</t>
+          <t>145381.994219881</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>161767.576</t>
+          <t>136976.405454252</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>157505.086</t>
+          <t>149877.465676238</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>185656.69</t>
+          <t>185578.561508121</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>185547.432</t>
+          <t>210743.792381888</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>204678.013</t>
+          <t>215298.41297581</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>200299.958</t>
+          <t>225476.100933943</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>184095.853</t>
+          <t>264880.656011057</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>159773.406</t>
+          <t>280324.241073704</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>104395.907</t>
+          <t>237231.086161039</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-89.81</t>
+          <t>545298.549566519</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-89.76</t>
+          <t>595671.882688816</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-87.16</t>
+          <t>546296.317448332</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-88.35</t>
+          <t>550559.584078313</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-90.7</t>
+          <t>559827.924355327</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-93.28</t>
+          <t>546059.288310521</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-93.55</t>
+          <t>516590.591712231</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-93.41</t>
+          <t>572674.271663728</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-94.52</t>
+          <t>700425.904121031</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-94.47</t>
+          <t>789646.203294406</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-95.05</t>
+          <t>808590.697184944</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-94.58</t>
+          <t>855373.532513009</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-94.05</t>
+          <t>985730.606451543</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-92.97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-90.48</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>28.683</t>
+          <t>143141.090244378</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>23.506</t>
+          <t>149845.764626259</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20.671</t>
+          <t>153009.12433474</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>22.691</t>
+          <t>158833.376482047</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>30.592</t>
+          <t>162872.121386245</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>43.99</t>
+          <t>178176.232055176</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>48.599</t>
+          <t>190976.721517479</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>38.267</t>
+          <t>196148.574637276</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>37.799</t>
+          <t>198444.141333506</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>30.463</t>
+          <t>204866.178068768</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>31.975</t>
+          <t>215662.279492884</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>31.026</t>
+          <t>220237.056421005</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>22.404</t>
+          <t>233223.897723086</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>16.988</t>
+          <t>236013.372408089</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>13.841</t>
+          <t>228839.713418951</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>133127.784362746</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>139368.926890817</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>142042.186841521</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>147728.752951229</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>151644.686131021</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>166730.278943514</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>179849.433456003</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>185100.922674331</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>187522.568122355</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>193222.90210259</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>201851.287700017</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>207426.50935102</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>220500.176045215</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>223347.6713283</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>215879.258804695</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>77885.4834856216</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>80079.3743283085</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>74998.0413001609</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>75463.020580724</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>79888.9132679466</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>72502.466580119</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>62644.4118557478</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>70534.6420237624</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>90772.7903018787</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>107491.992148112</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>109857.58426419</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>124546.720426057</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>140964.435688943</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>150830.402136296</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>116473.816238961</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>8901362512.59136</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>9177040074.49592</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>9007128540.90429</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>9254751724.46151</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>9684217187.03629</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>10212891029.1434</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10427860021.4307</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>10381982019.2324</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>10172976768.5968</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>10256930756.506</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>10132503196.9945</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>10855812843.4152</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>10952773572.5305</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>11238977126.2814</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>9939793337.42222</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>9570885152.2757</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>9849663323.61032</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>9683784563.11233</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>9952623526.6265</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>10405951101.7526</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>10925685308.8274</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>11103763203.8534</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>11039279586.4038</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>10807730727.5431</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>10916721518.0193</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>10817626230.5757</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>11568332438.2261</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>11671423986.3387</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>11327789120.3176</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>10896691842.5661</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>5381391824.60203</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>5506852282.72344</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>5387092140.93919</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>5490289994.89609</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>5682604777.80184</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>5874535449.51945</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>6007212809.69997</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>6010703694.68137</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>5908483300.80836</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>5927414080.1653</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>5813128087.68492</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>6143240852.99579</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>6195302899.769</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>6056673204.73946</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>5828056926.21779</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4128899.99999584</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4095799.9999959</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4043200</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4111400</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4197700.00000615</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4300700.00000532</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4391200</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4393300.00000522</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4367900</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4337400</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4348900</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4422500</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4524300</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4541646.26335567</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4424861.28133468</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3847799.99999621</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3819099.99999627</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3768000</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3836300</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3917600.00000346</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4022900</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4123600</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>4134200.00000303</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>4127600</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>4091200</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4103200</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>4170400</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>4267900</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>4320700</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>4228338.56512301</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>6772819999.99282</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>6770689999.99285</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>6703500000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>6809790000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>6988380000.0107</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>7061950000.00911</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>7105700000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>7006600000.00862</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>6908100000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6963430000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6979960000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>7.072e+09</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>7319330000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>7362323182.22011</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>7146911162.50548</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>6234639999.99358</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6244229999.9936</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>6174710000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>6277920000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>6444150000.00593</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6539080000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6609930000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>6527400000.00494</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>6446220000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>6489130000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>6490820000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>6587610000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>6822760000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>6920380000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>6705669998.77628</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.175632394391622</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.178519764421943</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.182521612994752</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.185480918571493</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.199769360570896</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.218077092896323</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.225195429041695</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.231065372362702</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.22077703781729</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.238035604533249</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.249053314488781</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.25943802992654</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.262575913097484</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.27981093651643</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.292918479894697</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.568263560293997</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.574674634470877</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.580260119671008</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.586000513061219</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.574163857675759</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.582930939050782</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.583532617697635</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.584072145887833</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.583415741425941</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.585317212081492</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.581267224553589</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.574570886085595</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.570379798923343</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.561167767493832</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.530134638009854</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.256104045314381</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.24680560110718</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.23721826733424</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.228518568367287</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.226066781753345</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.198991968052896</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.19127195326067</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.184862481749466</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.195807220756769</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.176647183385259</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.16967946095763</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.165991083987865</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.167044287979174</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.159021295989738</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.176946882095448</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.127366819728121</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.129160847897513</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.133416182165984</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.137055627698075</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.1464484811306</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.164891415642487</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.172730142899479</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.176779161263421</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.179782694531231</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.187163260028709</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.198873353722608</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.210336155623757</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.215609489132964</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.230321399524585</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.240881984702742</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.585702966243725</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.591529283873456</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.597372678209279</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.602366870709266</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.594291764382177</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.607277147009464</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.609096810665625</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.610223712014477</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.614762393708153</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.612470415297403</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.609644581664782</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.603618796500982</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.603726782905289</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.598529920241151</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.566309634240847</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.286930214028155</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.279309868229031</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.269211139624737</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.26057750159266</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.259259754487222</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.227831437348049</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.218173046434896</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.212997126722102</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.205454911760616</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.200366324673888</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.19148206461261</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.186045047875261</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.180663727961747</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.171148680234264</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.192808381056411</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>461976.65331</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>501511.41338</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>466168.81334</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>468861.31007</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>476120.03486</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>466126.22559</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>430428.36138</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>466075.03516</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>573860.72027</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>666076.61884</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>694302.57719</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>753739.90604</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>880097.95041</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>949568.28984</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>757060.99647</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>221026.57373</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>241622.0427</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>222083.29063</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>222828.18396</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>226402.71934</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>217884.4608</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>199620.81731</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>220412.1077</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>276351.35181</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>318235.78453</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>325155.99724</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>350022.82136</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>405845.0917</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>431154.64321</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>353704.9024</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3883063.05764445</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4018765.57132922</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>4144897.71115209</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>4291173.96676717</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>4451909.0550342</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4621620.99180891</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4765026.77031318</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>4883940.32262649</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>5000945.27065932</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>5138989.3150617</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>5306922.67425119</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>5502674.76391365</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>5725293.18762794</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
